--- a/datasets/day1_excel_foundations/02_formatting_cells_and_numbers/practice_completed.xlsx
+++ b/datasets/day1_excel_foundations/02_formatting_cells_and_numbers/practice_completed.xlsx
@@ -458,7 +458,7 @@
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
     <col width="16.5" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="19.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kwekwe</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -590,12 +590,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Mutare</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kwekwe</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Nairobi</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kwekwe</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chitungwiza</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Seattle</t>
+          <t>Mutare</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Harare</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -950,12 +950,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Miami</t>
+          <t>Kwekwe</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chitungwiza</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
+          <t>Lusaka</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
